--- a/file_testing/Template_Data_Mapel_Rapi.xlsx
+++ b/file_testing/Template_Data_Mapel_Rapi.xlsx
@@ -1,58 +1,195 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <workbookPr codeName="ThisWorkbook"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
+  <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
   <sheets>
-    <sheet name="Data Mapel" sheetId="1" r:id="rId1"/>
+    <sheet sheetId="1" name="Data Mapel" state="visible" r:id="rId4"/>
   </sheets>
+  <calcPr calcId="171027"/>
 </workbook>
 </file>
 
-<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
-  <metadataTypes count="1">
-    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
-  </metadataTypes>
-  <futureMetadata name="XLDAPR" count="1">
-    <bk>
-      <extLst>
-        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
-          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
-        </ext>
-      </extLst>
-    </bk>
-  </futureMetadata>
-  <cellMetadata count="1">
-    <bk>
-      <rc t="1" v="0"/>
-    </bk>
-  </cellMetadata>
-</metadata>
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="43">
+  <si>
+    <t>No</t>
+  </si>
+  <si>
+    <t>Mata Pelajaran</t>
+  </si>
+  <si>
+    <t>Pendidikan Agama Islam</t>
+  </si>
+  <si>
+    <t>Pendidikan Pancasila</t>
+  </si>
+  <si>
+    <t>Bahasa Indonesia</t>
+  </si>
+  <si>
+    <t>Pendidikan Jasmani, Olahraga, dan Kesehatan</t>
+  </si>
+  <si>
+    <t>Sejarah</t>
+  </si>
+  <si>
+    <t>Seni Budaya</t>
+  </si>
+  <si>
+    <t>Bahasa Inggris</t>
+  </si>
+  <si>
+    <t>Matematika</t>
+  </si>
+  <si>
+    <t>Informatika</t>
+  </si>
+  <si>
+    <t>Dasar Program Keahlian</t>
+  </si>
+  <si>
+    <t>Koding &amp; Kecerdasan Artifisial</t>
+  </si>
+  <si>
+    <t>Spreadsheet</t>
+  </si>
+  <si>
+    <t>Komputer Akuntansi (Accurate)</t>
+  </si>
+  <si>
+    <t>Muatan Lokal (Personal Branding)</t>
+  </si>
+  <si>
+    <t>K3LH</t>
+  </si>
+  <si>
+    <t>Akuntansi Keuangan</t>
+  </si>
+  <si>
+    <t>Akuntansi Lembaga</t>
+  </si>
+  <si>
+    <t>PKK</t>
+  </si>
+  <si>
+    <t>Ekonomi Bisnis dan Administrasi</t>
+  </si>
+  <si>
+    <t>Akuntansi Manufaktur</t>
+  </si>
+  <si>
+    <t>Perpajakan</t>
+  </si>
+  <si>
+    <t>Akuntansi Dasar</t>
+  </si>
+  <si>
+    <t>Akuntansi Jasa Dagang</t>
+  </si>
+  <si>
+    <t>Pengelolaan Keuangan</t>
+  </si>
+  <si>
+    <t>Pengelolaan Sarpras</t>
+  </si>
+  <si>
+    <t>Pengelolaan SDM</t>
+  </si>
+  <si>
+    <t>Pengelolaan Humas dan Keprotokolan</t>
+  </si>
+  <si>
+    <t>Logistik</t>
+  </si>
+  <si>
+    <t>Komunikasi di Tempat Kerja</t>
+  </si>
+  <si>
+    <t>Pengelolaan Administrasi Umum</t>
+  </si>
+  <si>
+    <t>Bahasa Sunda</t>
+  </si>
+  <si>
+    <t>Bahasa Jepang</t>
+  </si>
+  <si>
+    <t>Food &amp; Beverage Service</t>
+  </si>
+  <si>
+    <t>Front Office</t>
+  </si>
+  <si>
+    <t>Housekeeping</t>
+  </si>
+  <si>
+    <t>Laundry</t>
+  </si>
+  <si>
+    <t>Desain Komunikasi Visual</t>
+  </si>
+  <si>
+    <t>Fotografi</t>
+  </si>
+  <si>
+    <t>Videografi</t>
+  </si>
+  <si>
+    <t>Komputer Grafis</t>
+  </si>
+  <si>
+    <t>UI/UX Web Design</t>
+  </si>
+</sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:vt="http://schemas.openxmlformats.org/officeDocument/2006/docPropsVTypes">
-  <numFmts count="1">
-    <numFmt numFmtId="56" formatCode="&quot;上午/下午 &quot;hh&quot;時&quot;mm&quot;分&quot;ss&quot;秒 &quot;"/>
-  </numFmts>
-  <fonts count="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
-      <sz val="12"/>
       <color theme="1"/>
-      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <color rgb="FFFFFFFF"/>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <color rgb="FF1F2937"/>
+      <sz val="10.5"/>
+      <name val="Calibri"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1E40AF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF9FAFB"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -60,18 +197,74 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF0F2B6B"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF0F2B6B"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF0F2B6B"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FF0F2B6B"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFE5E7EB"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFE5E7EB"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFE5E7EB"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFE5E7EB"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+  <cellXfs count="7">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleMedium4"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -396,225 +589,352 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A42"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:B42"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
-    <col min="1" max="1" width="45.83203125" customWidth="1"/>
+    <col min="1" max="1" width="8" customWidth="1"/>
+    <col min="2" max="2" width="45" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="str">
-        <v>Mata Pelajaran</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="str">
-        <v>Pendidikan Agama Islam</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v>Pendidikan Pancasila</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="str">
-        <v>Bahasa Indonesia</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="str">
-        <v>Pendidikan Jasmani, Olahraga, dan Kesehatan</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="str">
-        <v>Sejarah</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="str">
-        <v>Seni Budaya</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="str">
-        <v>Bahasa Inggris</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="str">
-        <v>Matematika</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="str">
-        <v>Informatika</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="str">
-        <v>Dasar Program Keahlian</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="str">
-        <v>Koding &amp; Kecerdasan Artifisial</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="str">
-        <v>Spreadsheet</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="str">
-        <v>Komputer Akuntansi (Accurate)</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="str">
-        <v>Muatan Lokal (Personal Branding)</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="str">
-        <v>K3LH</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="str">
-        <v>Akuntansi Keuangan</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="str">
-        <v>Akuntansi Lembaga</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="str">
-        <v>PKK</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="str">
-        <v>Ekonomi Bisnis dan Administrasi</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="str">
-        <v>Akuntansi Manufaktur</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="str">
-        <v>Perpajakan</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="str">
-        <v>Akuntansi Dasar</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="str">
-        <v>Akuntansi Jasa Dagang</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="str">
-        <v>Pengelolaan Keuangan</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="str">
-        <v>Pengelolaan Sarpras</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="str">
-        <v>Pengelolaan SDM</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="str">
-        <v>Pengelolaan Humas dan Keprotokolan</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="str">
-        <v>Logistik</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="str">
-        <v>Komunikasi di Tempat Kerja</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="str">
-        <v>Pengelolaan Administrasi Umum</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="str">
-        <v>Bahasa Sunda</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="str">
-        <v>Bahasa Jepang</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="str">
-        <v>Food &amp; Beverage Service</v>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="str">
-        <v>Front Office</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="str">
-        <v>Housekeeping</v>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="str">
-        <v>Laundry</v>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="str">
-        <v>Desain Komunikasi Visual</v>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="str">
-        <v>Fotografi</v>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="str">
-        <v>Videografi</v>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="str">
-        <v>Komputer Grafis</v>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="str">
-        <v>UI/UX Web Design</v>
+    <row r="1" ht="28" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2" ht="22" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A2" s="3">
+        <v>1</v>
+      </c>
+      <c r="B2" s="4" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="3" ht="22" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A3" s="5">
+        <v>2</v>
+      </c>
+      <c r="B3" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="4" ht="22" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A4" s="3">
+        <v>3</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="5" ht="22" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A5" s="5">
+        <v>4</v>
+      </c>
+      <c r="B5" s="6" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="6" ht="22" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A6" s="3">
+        <v>5</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="7" ht="22" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A7" s="5">
+        <v>6</v>
+      </c>
+      <c r="B7" s="6" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="8" ht="22" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A8" s="3">
+        <v>7</v>
+      </c>
+      <c r="B8" s="4" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="9" ht="22" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A9" s="5">
+        <v>8</v>
+      </c>
+      <c r="B9" s="6" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="10" ht="22" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A10" s="3">
+        <v>9</v>
+      </c>
+      <c r="B10" s="4" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="11" ht="22" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A11" s="5">
+        <v>10</v>
+      </c>
+      <c r="B11" s="6" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="12" ht="22" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A12" s="3">
+        <v>11</v>
+      </c>
+      <c r="B12" s="4" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="13" ht="22" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A13" s="5">
+        <v>12</v>
+      </c>
+      <c r="B13" s="6" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="14" ht="22" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A14" s="3">
+        <v>13</v>
+      </c>
+      <c r="B14" s="4" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="15" ht="22" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A15" s="5">
+        <v>14</v>
+      </c>
+      <c r="B15" s="6" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="16" ht="22" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A16" s="3">
+        <v>15</v>
+      </c>
+      <c r="B16" s="4" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="17" ht="22" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A17" s="5">
+        <v>16</v>
+      </c>
+      <c r="B17" s="6" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="18" ht="22" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A18" s="3">
+        <v>17</v>
+      </c>
+      <c r="B18" s="4" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="19" ht="22" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A19" s="5">
+        <v>18</v>
+      </c>
+      <c r="B19" s="6" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="20" ht="22" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A20" s="3">
+        <v>19</v>
+      </c>
+      <c r="B20" s="4" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="21" ht="22" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A21" s="5">
+        <v>20</v>
+      </c>
+      <c r="B21" s="6" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="22" ht="22" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A22" s="3">
+        <v>21</v>
+      </c>
+      <c r="B22" s="4" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="23" ht="22" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A23" s="5">
+        <v>22</v>
+      </c>
+      <c r="B23" s="6" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="24" ht="22" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A24" s="3">
+        <v>23</v>
+      </c>
+      <c r="B24" s="4" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="25" ht="22" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A25" s="5">
+        <v>24</v>
+      </c>
+      <c r="B25" s="6" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="26" ht="22" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A26" s="3">
+        <v>25</v>
+      </c>
+      <c r="B26" s="4" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="27" ht="22" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A27" s="5">
+        <v>26</v>
+      </c>
+      <c r="B27" s="6" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="28" ht="22" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A28" s="3">
+        <v>27</v>
+      </c>
+      <c r="B28" s="4" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="29" ht="22" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A29" s="5">
+        <v>28</v>
+      </c>
+      <c r="B29" s="6" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="30" ht="22" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A30" s="3">
+        <v>29</v>
+      </c>
+      <c r="B30" s="4" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="31" ht="22" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A31" s="5">
+        <v>30</v>
+      </c>
+      <c r="B31" s="6" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="32" ht="22" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A32" s="3">
+        <v>31</v>
+      </c>
+      <c r="B32" s="4" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="33" ht="22" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A33" s="5">
+        <v>32</v>
+      </c>
+      <c r="B33" s="6" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="34" ht="22" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A34" s="3">
+        <v>33</v>
+      </c>
+      <c r="B34" s="4" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="35" ht="22" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A35" s="5">
+        <v>34</v>
+      </c>
+      <c r="B35" s="6" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="36" ht="22" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A36" s="3">
+        <v>35</v>
+      </c>
+      <c r="B36" s="4" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="37" ht="22" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A37" s="5">
+        <v>36</v>
+      </c>
+      <c r="B37" s="6" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="38" ht="22" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A38" s="3">
+        <v>37</v>
+      </c>
+      <c r="B38" s="4" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="39" ht="22" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A39" s="5">
+        <v>38</v>
+      </c>
+      <c r="B39" s="6" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="40" ht="22" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A40" s="3">
+        <v>39</v>
+      </c>
+      <c r="B40" s="4" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="41" ht="22" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A41" s="5">
+        <v>40</v>
+      </c>
+      <c r="B41" s="6" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="42" ht="22" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A42" s="3">
+        <v>41</v>
+      </c>
+      <c r="B42" s="4" t="s">
+        <v>42</v>
       </c>
     </row>
   </sheetData>
-  <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:A42"/>
-  </ignoredErrors>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>
 </file>